--- a/Sensors.xlsx
+++ b/Sensors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TEMP\CHUD-MCU-SENSORS-PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B61A5F-4D5D-4F89-9CCC-24893544CD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{796B764A-8EAC-45A1-ABCE-033245D38B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C876397A-FBC0-4325-9432-4323EC888558}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="61">
   <si>
     <t>Comment</t>
   </si>
@@ -219,6 +219,9 @@
   </si>
   <si>
     <t>https://www.digikey.co.nz/en/products/detail/stmicroelectronics/LSM6DSO32TR/11694177?s=N4IgTCBcDaIDIGUCyA2AIgg8gZjAFQCUQBdAXyA</t>
+  </si>
+  <si>
+    <t>we already have these</t>
   </si>
 </sst>
 </file>
@@ -234,7 +237,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +259,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
@@ -300,6 +309,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2368766F-F6C5-40C2-ADB3-B97D5BA14A7D}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="19.125" bestFit="1" customWidth="1"/>
@@ -670,7 +681,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -691,7 +702,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -714,7 +725,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -802,7 +813,7 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -871,7 +882,7 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -926,6 +937,12 @@
       <c r="A16" s="7"/>
       <c r="B16" s="11" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="13"/>
+      <c r="B17" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
